--- a/per-stock/SNPS/financials.xlsx
+++ b/per-stock/SNPS/financials.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (annual)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (quarterly)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance sheet (annual)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (annual)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data flags" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FY Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Income stmt (annual)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Income stmt (quarterly)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Balance sheet (annual)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Balance sheet (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cash flow (annual)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cash flow (quarterly)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Data flags" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -61,11 +67,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,7 +540,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>96244596736</v>
+        <v>87220748288</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -546,7 +555,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>104908840960</v>
+        <v>95577202688</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -561,7 +570,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>76.94028</v>
+        <v>104.2357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -576,7 +585,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29.457893</v>
+        <v>26.412212</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -591,7 +600,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12.019065</v>
+        <v>10.049191</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -606,7 +615,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.82024</v>
+        <v>0.82598996</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -621,7 +630,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.13340001</v>
+        <v>0.10383</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -636,7 +645,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.13756</v>
+        <v>0.089090005</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -651,7 +660,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.055430003</v>
+        <v>0.03824</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -666,7 +675,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.655</v>
+        <v>0.419</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -681,7 +690,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2203482112</v>
+        <v>2484438016</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -696,7 +705,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10868556800</v>
+        <v>10841960448</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -711,11 +720,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3096222464</v>
+        <v>2633795000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>yfinance info.freeCashflow</t>
+          <t>statement: TTM OCF - |capex| (yfinance quarterly_cashflow)</t>
         </is>
       </c>
     </row>
@@ -726,7 +735,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>191562027</v>
+        <v>191479325</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -741,7 +750,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>502.42</v>
+        <v>455.51</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -785,6 +794,477 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fiscal-year summary (GAAP, $ except where noted)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FY-3</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FY-2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FY-1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TTM</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source / formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fiscal period end</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2023-10-31</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TTM → 2026-04-30</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>annual statement headers; TTM = Σ last 4 quarters</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>'Income stmt (annual)'!D55</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>'Income stmt (annual)'!C55</f>
+        <v/>
+      </c>
+      <c r="D3" s="3">
+        <f>'Income stmt (annual)'!B55</f>
+        <v/>
+      </c>
+      <c r="E3" s="3">
+        <f>SUM('Income stmt (quarterly)'!B55:E55)</f>
+        <v/>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>'Income stmt (annual)'!D53</f>
+        <v/>
+      </c>
+      <c r="C4" s="3">
+        <f>'Income stmt (annual)'!C53</f>
+        <v/>
+      </c>
+      <c r="D4" s="3">
+        <f>'Income stmt (annual)'!B53</f>
+        <v/>
+      </c>
+      <c r="E4" s="3">
+        <f>SUM('Income stmt (quarterly)'!B53:E53)</f>
+        <v/>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gross Profit (GAAP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B5" s="4">
+        <f>IFERROR(B4/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C5" s="4">
+        <f>IFERROR(C4/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="4">
+        <f>IFERROR(D4/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="4">
+        <f>IFERROR(E4/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>GAAP = gross profit / revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>'Income stmt (annual)'!D42</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>'Income stmt (annual)'!C42</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>'Income stmt (annual)'!B42</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>SUM('Income stmt (quarterly)'!B42:E42)</f>
+        <v/>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
+        <f>IFERROR(B6/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="4">
+        <f>IFERROR(C6/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="4">
+        <f>IFERROR(D6/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="4">
+        <f>IFERROR(E6/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f> operating income / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>'Income stmt (annual)'!D10</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>'Income stmt (annual)'!C10</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>'Income stmt (annual)'!B10</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>SUM('Income stmt (quarterly)'!B10:E10)</f>
+        <v/>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Free cash flow</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>'Cash flow (annual)'!D2</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>'Cash flow (annual)'!C2</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>'Cash flow (annual)'!B2</f>
+        <v/>
+      </c>
+      <c r="E9" s="3">
+        <f>SUM('Cash flow (quarterly)'!B2:E2)</f>
+        <v/>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FCF = OCF − capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FCF margin %</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <f>IFERROR(B9/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="4">
+        <f>IFERROR(C9/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="4">
+        <f>IFERROR(D9/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="4">
+        <f>IFERROR(E9/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f> FCF / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>-'Cash flow (annual)'!D7</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>-'Cash flow (annual)'!C7</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>-'Cash flow (annual)'!B7</f>
+        <v/>
+      </c>
+      <c r="E11" s="3">
+        <f>-SUM('Cash flow (quarterly)'!B7:E7)</f>
+        <v/>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Capex (shown positive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Capex / revenue %</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <f>IFERROR(B11/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="4">
+        <f>IFERROR(C11/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="4">
+        <f>IFERROR(D11/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="4">
+        <f>IFERROR(E11/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f> capex / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Net debt</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>'Balance sheet (annual)'!D5</f>
+        <v/>
+      </c>
+      <c r="C13" s="3">
+        <f>'Balance sheet (annual)'!C5</f>
+        <v/>
+      </c>
+      <c r="D13" s="3">
+        <f>'Balance sheet (annual)'!B5</f>
+        <v/>
+      </c>
+      <c r="E13" s="3">
+        <f>'Balance sheet (quarterly)'!B5</f>
+        <v/>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Net debt; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="B14" s="5">
+        <f>IFERROR(B13/B8,"")</f>
+        <v/>
+      </c>
+      <c r="C14" s="5">
+        <f>IFERROR(C13/C8,"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>IFERROR(D13/D8,"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>IFERROR(E13/E8,"")</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f> net debt / EBITDA</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Share count (period-end, M)</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <f>'Balance sheet (annual)'!D3/1e6</f>
+        <v/>
+      </c>
+      <c r="C15" s="6">
+        <f>'Balance sheet (annual)'!C3/1e6</f>
+        <v/>
+      </c>
+      <c r="D15" s="6">
+        <f>'Balance sheet (annual)'!B3/1e6</f>
+        <v/>
+      </c>
+      <c r="E15" s="6">
+        <f>'Balance sheet (quarterly)'!B3/1e6</f>
+        <v/>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>shares ÷ 1e6; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Share count YoY %</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4">
+        <f>IFERROR(C15/B15-1,"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="4">
+        <f>IFERROR(D15/C15-1,"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="4">
+        <f>IFERROR(E15/D15-1,"")</f>
+        <v/>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vs prior period</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1875,13 +2355,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1891,6 +2371,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1901,30 +2382,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-10-31</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-07-31</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-04-30</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2025-01-31</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024-10-31</t>
         </is>
@@ -1937,21 +2423,22 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>-14679500</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>-22463910</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>72435512.351798</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>4410</v>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>5803868</v>
-      </c>
       <c r="F2" s="3" t="n">
-        <v>13230</v>
+        <v>5808086.836904</v>
       </c>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1960,21 +2447,22 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>0.181</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>0.131787</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>0.21</v>
       </c>
-      <c r="E3" s="3" t="n">
-        <v>0.119</v>
-      </c>
       <c r="F3" s="3" t="n">
-        <v>0.21</v>
+        <v>0.119087</v>
       </c>
       <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1983,21 +2471,22 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>726565000</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>816566000</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>610757000</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>450260000</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="F4" s="3" t="n">
         <v>490659000</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>350127000</v>
-      </c>
       <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2006,21 +2495,22 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>-117436000</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>-124110000</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>549642000</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>21000</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="F5" s="3" t="n">
         <v>48772000</v>
       </c>
-      <c r="F5" s="3" t="n">
-        <v>63000</v>
-      </c>
       <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2029,21 +2519,22 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>-117436000</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>-124110000</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>549642000</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>21000</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="F6" s="3" t="n">
         <v>48772000</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>63000</v>
-      </c>
       <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2052,21 +2543,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>17105000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>64474000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>448696000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>242509000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>349232000</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>295683000</v>
-      </c>
       <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2075,21 +2567,22 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>456489000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>450688000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>449123000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>114469000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>48904000</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>47934000</v>
-      </c>
       <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2098,21 +2591,22 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>328636000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>342687000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>361496000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>294668000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>273439000</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>226041000</v>
-      </c>
       <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2121,21 +2615,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>609129000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>692456000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>1160399000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>450281000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>539431000</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>350190000</v>
-      </c>
       <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2144,21 +2639,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>152640000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>241768000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>711276000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>335812000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>490527000</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>302256000</v>
-      </c>
       <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2167,21 +2663,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>-120479000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>-145282000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>-174095000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>-15085000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>-4446000</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>24582000</v>
-      </c>
       <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2190,21 +2687,22 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>133364000</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>162715000</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>194752000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>146502000</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>94336000</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>11139000</v>
-      </c>
       <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2213,21 +2711,22 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>12885000</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>17433000</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>20657000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>131417000</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>89890000</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>35721000</v>
-      </c>
       <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2236,21 +2735,22 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>119861500</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>166120090</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>-28510487.648202</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>242492410</v>
       </c>
-      <c r="E15" s="3" t="n">
-        <v>306263868</v>
-      </c>
       <c r="F15" s="3" t="n">
-        <v>295633230</v>
+        <v>306268086.836904</v>
       </c>
       <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2259,21 +2759,22 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>17105000</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>64958000</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>448696000</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="E16" s="3" t="n">
         <v>242509000</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="F16" s="3" t="n">
         <v>345332000</v>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>295683000</v>
-      </c>
       <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2282,21 +2783,22 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
+        <v>2039665000</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>2087470000</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="D17" s="3" t="n">
         <v>2133467000</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>1574468000</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="F17" s="3" t="n">
         <v>1227840000</v>
       </c>
-      <c r="F17" s="3" t="n">
-        <v>1203476000</v>
-      </c>
       <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2305,21 +2807,22 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
+        <v>120426000</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>203046000</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>121393000</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>165269000</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="F18" s="3" t="n">
         <v>376426000</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>251839000</v>
-      </c>
       <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2328,21 +2831,22 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
+        <v>192144000</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>190762000</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="D19" s="3" t="n">
         <v>187502000</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>161682000</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>156088000</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>156189000</v>
-      </c>
       <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2351,21 +2855,22 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
+        <v>191464000</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>189593000</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>185779000</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>160174000</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>154927000</v>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>154408000</v>
-      </c>
       <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2374,21 +2879,22 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="C21" s="3" t="n">
         <v>0.34</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="D21" s="3" t="n">
         <v>2.39</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="F21" s="3" t="n">
         <v>2.21</v>
       </c>
-      <c r="F21" s="3" t="n">
-        <v>1.89</v>
-      </c>
       <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2397,21 +2903,22 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>0.34</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>2.42</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>1.51</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>2.23</v>
       </c>
-      <c r="F22" s="3" t="n">
-        <v>1.91</v>
-      </c>
       <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2420,21 +2927,22 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>17105000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>64958000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>448696000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>242509000</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>345332000</v>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>295683000</v>
-      </c>
       <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2443,21 +2951,22 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>17105000</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>64958000</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>448696000</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>242509000</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="F24" s="3" t="n">
         <v>345332000</v>
       </c>
-      <c r="F24" s="3" t="n">
-        <v>295683000</v>
-      </c>
       <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2466,21 +2975,22 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
+        <v>17105000</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>64958000</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="D25" s="3" t="n">
         <v>448696000</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="E25" s="3" t="n">
         <v>242509000</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="F25" s="3" t="n">
         <v>345332000</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>295683000</v>
-      </c>
       <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2489,21 +2999,22 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
+        <v>237000</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>-242000</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>243000</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E26" s="3" t="n">
         <v>232000</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="F26" s="3" t="n">
         <v>222000</v>
       </c>
-      <c r="F26" s="3" t="n">
-        <v>-1728000</v>
-      </c>
       <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2512,21 +3023,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
+        <v>16868000</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>65200000</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>448453000</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="E27" s="3" t="n">
         <v>242277000</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="F27" s="3" t="n">
         <v>345110000</v>
       </c>
-      <c r="F27" s="3" t="n">
-        <v>297411000</v>
-      </c>
       <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2535,21 +3047,22 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>484000</v>
-      </c>
-      <c r="C28" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="3" t="n">
         <v>-3900000</v>
       </c>
-      <c r="F28" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2558,21 +3071,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
+        <v>16868000</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>64716000</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>448453000</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>242277000</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>349010000</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>297411000</v>
-      </c>
       <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2581,21 +3095,22 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
+        <v>2408000</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>14337000</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="D30" s="3" t="n">
         <v>68071000</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="E30" s="3" t="n">
         <v>-52967000</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="F30" s="3" t="n">
         <v>47181000</v>
       </c>
-      <c r="F30" s="3" t="n">
-        <v>-6294000</v>
-      </c>
       <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2604,21 +3119,22 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
+        <v>19276000</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>79053000</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="D31" s="3" t="n">
         <v>516524000</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>189310000</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="F31" s="3" t="n">
         <v>396191000</v>
       </c>
-      <c r="F31" s="3" t="n">
-        <v>291117000</v>
-      </c>
       <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2627,21 +3143,22 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
+        <v>-96565000</v>
+      </c>
+      <c r="C32" s="3" t="n">
         <v>-96993000</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="D32" s="3" t="n">
         <v>569226000</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="E32" s="3" t="n">
         <v>39126000</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="F32" s="3" t="n">
         <v>24211000</v>
       </c>
-      <c r="F32" s="3" t="n">
-        <v>14696000</v>
-      </c>
       <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2650,21 +3167,22 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
+        <v>20871000</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>27117000</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="D33" s="3" t="n">
         <v>19584000</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="E33" s="3" t="n">
         <v>39105000</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="F33" s="3" t="n">
         <v>-24561000</v>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>14633000</v>
-      </c>
       <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2673,21 +3191,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
+        <v>-115894000</v>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>-118282000</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="D34" s="3" t="n">
         <v>548906000</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="E34" s="3" t="n">
         <v>-1200000</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="F34" s="3" t="n">
         <v>48950000</v>
       </c>
-      <c r="F34" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2695,18 +3214,21 @@
           <t>Gain On Sale Of Ppe</t>
         </is>
       </c>
-      <c r="B35" s="3" t="n"/>
-      <c r="C35" s="3" t="n">
+      <c r="B35" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="C35" s="3" t="n"/>
       <c r="D35" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3" t="n">
         <v>51385000</v>
       </c>
-      <c r="F35" s="3" t="n"/>
       <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2714,22 +3236,23 @@
           <t>Gain On Sale Of Business</t>
         </is>
       </c>
-      <c r="B36" s="3" t="n"/>
-      <c r="C36" s="3" t="n">
+      <c r="B36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="3" t="n"/>
+      <c r="D36" s="3" t="n">
         <v>548906000</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>-1200000</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>-2435000</v>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="H36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2738,9 +3261,11 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>115894000</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>118282000</v>
       </c>
-      <c r="C37" s="3" t="n"/>
       <c r="D37" s="3" t="n"/>
       <c r="E37" s="3" t="n"/>
       <c r="F37" s="3" t="n">
@@ -2749,6 +3274,9 @@
       <c r="G37" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="H37" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2757,21 +3285,22 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
+        <v>-1542000</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>-5828000</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="D38" s="3" t="n">
         <v>736000</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="E38" s="3" t="n">
         <v>1221000</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="F38" s="3" t="n">
         <v>-178000</v>
       </c>
-      <c r="F38" s="3" t="n">
-        <v>63000</v>
-      </c>
       <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2780,21 +3309,22 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
+        <v>-120479000</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>-145282000</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="D39" s="3" t="n">
         <v>-174095000</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="E39" s="3" t="n">
         <v>-15085000</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="F39" s="3" t="n">
         <v>-4446000</v>
       </c>
-      <c r="F39" s="3" t="n">
-        <v>24582000</v>
-      </c>
       <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2803,21 +3333,22 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
+        <v>133364000</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>162715000</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>194752000</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>146502000</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="F40" s="3" t="n">
         <v>94336000</v>
       </c>
-      <c r="F40" s="3" t="n">
-        <v>11139000</v>
-      </c>
       <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2826,21 +3357,22 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
+        <v>12885000</v>
+      </c>
+      <c r="C41" s="3" t="n">
         <v>17433000</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="D41" s="3" t="n">
         <v>20657000</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="E41" s="3" t="n">
         <v>131417000</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="F41" s="3" t="n">
         <v>89890000</v>
       </c>
-      <c r="F41" s="3" t="n">
-        <v>35721000</v>
-      </c>
       <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2849,21 +3381,22 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
+        <v>236320000</v>
+      </c>
+      <c r="C42" s="3" t="n">
         <v>321328000</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="D42" s="3" t="n">
         <v>121393000</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="E42" s="3" t="n">
         <v>165269000</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="F42" s="3" t="n">
         <v>376426000</v>
       </c>
-      <c r="F42" s="3" t="n">
-        <v>251839000</v>
-      </c>
       <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2872,21 +3405,22 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
+        <v>1409815000</v>
+      </c>
+      <c r="C43" s="3" t="n">
         <v>1450088000</v>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="D43" s="3" t="n">
         <v>1478804000</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="E43" s="3" t="n">
         <v>1193904000</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="F43" s="3" t="n">
         <v>909493000</v>
       </c>
-      <c r="F43" s="3" t="n">
-        <v>933501000</v>
-      </c>
       <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2895,21 +3429,22 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
+        <v>155275000</v>
+      </c>
+      <c r="C44" s="3" t="n">
         <v>155993000</v>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="D44" s="3" t="n">
         <v>155956000</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="E44" s="3" t="n">
         <v>28573000</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="F44" s="3" t="n">
         <v>3996000</v>
       </c>
-      <c r="F44" s="3" t="n">
-        <v>4000000</v>
-      </c>
       <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2918,21 +3453,22 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
+        <v>155275000</v>
+      </c>
+      <c r="C45" s="3" t="n">
         <v>155993000</v>
       </c>
-      <c r="C45" s="3" t="n">
+      <c r="D45" s="3" t="n">
         <v>155956000</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="E45" s="3" t="n">
         <v>28573000</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="F45" s="3" t="n">
         <v>3996000</v>
       </c>
-      <c r="F45" s="3" t="n">
-        <v>4000000</v>
-      </c>
       <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2941,21 +3477,22 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
+        <v>155275000</v>
+      </c>
+      <c r="C46" s="3" t="n">
         <v>155993000</v>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="D46" s="3" t="n">
         <v>155956000</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="E46" s="3" t="n">
         <v>28573000</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="F46" s="3" t="n">
         <v>3996000</v>
       </c>
-      <c r="F46" s="3" t="n">
-        <v>4000000</v>
-      </c>
       <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2964,21 +3501,22 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
+        <v>155275000</v>
+      </c>
+      <c r="C47" s="3" t="n">
         <v>155993000</v>
       </c>
-      <c r="C47" s="3" t="n">
+      <c r="D47" s="3" t="n">
         <v>155956000</v>
       </c>
-      <c r="D47" s="3" t="n">
+      <c r="E47" s="3" t="n">
         <v>28573000</v>
       </c>
-      <c r="E47" s="3" t="n">
+      <c r="F47" s="3" t="n">
         <v>3996000</v>
       </c>
-      <c r="F47" s="3" t="n">
-        <v>4000000</v>
-      </c>
       <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2987,21 +3525,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
+        <v>700124000</v>
+      </c>
+      <c r="C48" s="3" t="n">
         <v>714988000</v>
       </c>
-      <c r="C48" s="3" t="n">
+      <c r="D48" s="3" t="n">
         <v>746842000</v>
       </c>
-      <c r="D48" s="3" t="n">
+      <c r="E48" s="3" t="n">
         <v>625301000</v>
       </c>
-      <c r="E48" s="3" t="n">
+      <c r="F48" s="3" t="n">
         <v>553979000</v>
       </c>
-      <c r="F48" s="3" t="n">
-        <v>553216000</v>
-      </c>
       <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3010,21 +3549,22 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
+        <v>554416000</v>
+      </c>
+      <c r="C49" s="3" t="n">
         <v>579107000</v>
       </c>
-      <c r="C49" s="3" t="n">
+      <c r="D49" s="3" t="n">
         <v>576006000</v>
       </c>
-      <c r="D49" s="3" t="n">
+      <c r="E49" s="3" t="n">
         <v>540030000</v>
       </c>
-      <c r="E49" s="3" t="n">
+      <c r="F49" s="3" t="n">
         <v>351518000</v>
       </c>
-      <c r="F49" s="3" t="n">
-        <v>376285000</v>
-      </c>
       <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3033,21 +3573,22 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
+        <v>381998000</v>
+      </c>
+      <c r="C50" s="3" t="n">
         <v>396375000</v>
       </c>
-      <c r="C50" s="3" t="n">
+      <c r="D50" s="3" t="n">
         <v>390491000</v>
       </c>
-      <c r="D50" s="3" t="n">
+      <c r="E50" s="3" t="n">
         <v>259480000</v>
       </c>
-      <c r="E50" s="3" t="n">
+      <c r="F50" s="3" t="n">
         <v>215021000</v>
       </c>
-      <c r="F50" s="3" t="n">
-        <v>209199000</v>
-      </c>
       <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3056,21 +3597,22 @@
         </is>
       </c>
       <c r="B51" s="3" t="n">
+        <v>172418000</v>
+      </c>
+      <c r="C51" s="3" t="n">
         <v>182732000</v>
       </c>
-      <c r="C51" s="3" t="n">
+      <c r="D51" s="3" t="n">
         <v>185515000</v>
       </c>
-      <c r="D51" s="3" t="n">
+      <c r="E51" s="3" t="n">
         <v>280550000</v>
       </c>
-      <c r="E51" s="3" t="n">
+      <c r="F51" s="3" t="n">
         <v>136497000</v>
       </c>
-      <c r="F51" s="3" t="n">
-        <v>167086000</v>
-      </c>
       <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3079,21 +3621,22 @@
         </is>
       </c>
       <c r="B52" s="3" t="n">
+        <v>172418000</v>
+      </c>
+      <c r="C52" s="3" t="n">
         <v>182732000</v>
       </c>
-      <c r="C52" s="3" t="n">
+      <c r="D52" s="3" t="n">
         <v>185515000</v>
       </c>
-      <c r="D52" s="3" t="n">
+      <c r="E52" s="3" t="n">
         <v>280550000</v>
       </c>
-      <c r="E52" s="3" t="n">
+      <c r="F52" s="3" t="n">
         <v>136497000</v>
       </c>
-      <c r="F52" s="3" t="n">
-        <v>167086000</v>
-      </c>
       <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3102,21 +3645,22 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
+        <v>1646135000</v>
+      </c>
+      <c r="C53" s="3" t="n">
         <v>1771416000</v>
       </c>
-      <c r="C53" s="3" t="n">
+      <c r="D53" s="3" t="n">
         <v>1600197000</v>
       </c>
-      <c r="D53" s="3" t="n">
+      <c r="E53" s="3" t="n">
         <v>1359173000</v>
       </c>
-      <c r="E53" s="3" t="n">
+      <c r="F53" s="3" t="n">
         <v>1285919000</v>
       </c>
-      <c r="F53" s="3" t="n">
-        <v>1185340000</v>
-      </c>
       <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3125,21 +3669,22 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
+        <v>629850000</v>
+      </c>
+      <c r="C54" s="3" t="n">
         <v>637382000</v>
       </c>
-      <c r="C54" s="3" t="n">
+      <c r="D54" s="3" t="n">
         <v>654663000</v>
       </c>
-      <c r="D54" s="3" t="n">
+      <c r="E54" s="3" t="n">
         <v>380564000</v>
       </c>
-      <c r="E54" s="3" t="n">
+      <c r="F54" s="3" t="n">
         <v>318347000</v>
       </c>
-      <c r="F54" s="3" t="n">
-        <v>269975000</v>
-      </c>
       <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3148,21 +3693,22 @@
         </is>
       </c>
       <c r="B55" s="3" t="n">
+        <v>2275985000</v>
+      </c>
+      <c r="C55" s="3" t="n">
         <v>2408798000</v>
       </c>
-      <c r="C55" s="3" t="n">
+      <c r="D55" s="3" t="n">
         <v>2254860000</v>
       </c>
-      <c r="D55" s="3" t="n">
+      <c r="E55" s="3" t="n">
         <v>1739737000</v>
       </c>
-      <c r="E55" s="3" t="n">
+      <c r="F55" s="3" t="n">
         <v>1604266000</v>
       </c>
-      <c r="F55" s="3" t="n">
-        <v>1455315000</v>
-      </c>
       <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3171,28 +3717,29 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
+        <v>2275985000</v>
+      </c>
+      <c r="C56" s="3" t="n">
         <v>2408798000</v>
       </c>
-      <c r="C56" s="3" t="n">
+      <c r="D56" s="3" t="n">
         <v>2254860000</v>
       </c>
-      <c r="D56" s="3" t="n">
+      <c r="E56" s="3" t="n">
         <v>1739737000</v>
       </c>
-      <c r="E56" s="3" t="n">
+      <c r="F56" s="3" t="n">
         <v>1604266000</v>
       </c>
-      <c r="F56" s="3" t="n">
-        <v>1455315000</v>
-      </c>
       <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4790,7 +5337,1766 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G78"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Treasury Shares Number</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>593000</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>589000</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>1222000</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>1756000</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>2115000</v>
+      </c>
+      <c r="G2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ordinary Shares Number</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>191444000</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>191449000</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>185994000</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>185460000</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>155146000</v>
+      </c>
+      <c r="G3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Share Issued</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>192037000</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>192038000</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>187216000</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>187216000</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>157261000</v>
+      </c>
+      <c r="G4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Net Debt</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>7623490000</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>7914638000</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>10596485000</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>11813658000</v>
+      </c>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Total Debt</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>10841960000</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>10868557000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>14293418000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>15140314000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>10742251000</v>
+      </c>
+      <c r="G6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Tangible Book Value</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>-8251094000</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>-8621591000</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>-11251204000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>-12411104000</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>6281052000</v>
+      </c>
+      <c r="G7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Invested Capital</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>40514093000</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>40593037000</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>41812117000</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>41954664000</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>19966361000</v>
+      </c>
+      <c r="G8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Working Capital</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>1646586000</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>1430988000</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>2289608000</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>2151421000</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>14472953000</v>
+      </c>
+      <c r="G9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Net Tangible Assets</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>-8251094000</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>-8621591000</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>-11251204000</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>-12411104000</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>6281052000</v>
+      </c>
+      <c r="G10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capital Lease Obligations</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>805998000</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>824347000</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>808903000</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>800181000</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>691608000</v>
+      </c>
+      <c r="G11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Common Stock Equity</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>30478131000</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>30548827000</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>28327602000</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>27614531000</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>9915718000</v>
+      </c>
+      <c r="G12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Total Capitalization</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>40491976000</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>40570920000</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>41790000000</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>41932547000</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>19943399000</v>
+      </c>
+      <c r="G13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Total Equity Gross Minority Interest</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>30477065000</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>30547998000</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>28327015000</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>27614186000</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>9915605000</v>
+      </c>
+      <c r="G14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Minority Interest</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>-1066000</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>-829000</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>-587000</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>-345000</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>-113000</v>
+      </c>
+      <c r="G15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Stockholders Equity</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>30478131000</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>30548827000</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>28327602000</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>27614531000</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>9915718000</v>
+      </c>
+      <c r="G16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Gains Losses Not Affecting Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>-244082000</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>-203683000</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>-232414000</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>-231895000</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>-240136000</v>
+      </c>
+      <c r="G17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Other Equity Adjustments</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>-244082000</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>-203683000</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>-232414000</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>-231895000</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>-240136000</v>
+      </c>
+      <c r="G18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Treasury Stock</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>242827000</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>191851000</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>398278000</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>572091000</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>689001000</v>
+      </c>
+      <c r="G19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>10397550000</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>10380445000</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>10315487000</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>9866791000</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>9624282000</v>
+      </c>
+      <c r="G20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Additional Paid In Capital</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>20565562000</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>20562001000</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>18640947000</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>18549871000</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>1219021000</v>
+      </c>
+      <c r="G21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Capital Stock</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>1928000</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>1915000</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>1860000</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>1855000</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>1552000</v>
+      </c>
+      <c r="G22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>1928000</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>1915000</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>1860000</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>1855000</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>1552000</v>
+      </c>
+      <c r="G23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Preferred Stock</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Total Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>16411962000</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>16689930000</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>19897446000</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>20616070000</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>13840912000</v>
+      </c>
+      <c r="G25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Total Non Current Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>12621330000</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>12747280000</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>16174952000</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>17171863000</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>11434836000</v>
+      </c>
+      <c r="G26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Other Non Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>201319000</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>194060000</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>200997000</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>182027000</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>99733000</v>
+      </c>
+      <c r="G27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Liabilities Heldfor Sale Non Current</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n"/>
+      <c r="C28" s="3" t="n"/>
+      <c r="D28" s="3" t="n"/>
+      <c r="E28" s="3" t="n"/>
+      <c r="F28" s="3" t="n"/>
+      <c r="G28" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>1735691000</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>1839878000</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>1830859000</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>1999091000</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>719984000</v>
+      </c>
+      <c r="G29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>389419000</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>420887000</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>382557000</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>383405000</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>331133000</v>
+      </c>
+      <c r="G30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Liabilities</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>877749000</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>954115000</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>1001070000</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>1188824000</v>
+      </c>
+      <c r="F31" s="3" t="n"/>
+      <c r="G31" s="3" t="n">
+        <v>36557000</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Long Term Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>10684320000</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>10713342000</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>14143096000</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>14990745000</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>10615119000</v>
+      </c>
+      <c r="G32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Long Term Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>670475000</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>691249000</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>680698000</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>672729000</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>587438000</v>
+      </c>
+      <c r="G33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Long Term Debt</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>10013845000</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>10022093000</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>13462398000</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>14318016000</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>10027681000</v>
+      </c>
+      <c r="G34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>3790632000</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>3942650000</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>3722494000</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>3444207000</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>2406076000</v>
+      </c>
+      <c r="G35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Other Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>27912000</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>23625000</v>
+      </c>
+      <c r="D36" s="3" t="n"/>
+      <c r="E36" s="3" t="n">
+        <v>20005000</v>
+      </c>
+      <c r="F36" s="3" t="n"/>
+      <c r="G36" s="3" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>2419876000</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>2459122000</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>2245961000</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>1991429000</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>1375398000</v>
+      </c>
+      <c r="G37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>2419876000</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>2459122000</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>2245961000</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>1991429000</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>1375398000</v>
+      </c>
+      <c r="G38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Current Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>157640000</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>155215000</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>150322000</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>149569000</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>127132000</v>
+      </c>
+      <c r="G39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Current Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>135523000</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>133098000</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>128205000</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>127452000</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>104170000</v>
+      </c>
+      <c r="G40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Current Debt</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>22117000</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>22117000</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>22117000</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>22117000</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>22962000</v>
+      </c>
+      <c r="G41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Other Current Borrowings</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>22117000</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>22117000</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>22117000</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>22117000</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>22962000</v>
+      </c>
+      <c r="G42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Payables And Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>1185204000</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>1304688000</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>1326211000</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>1283204000</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>903546000</v>
+      </c>
+      <c r="G43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Current Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>960927000</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>1079865000</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>1066781000</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>1133196000</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>699234000</v>
+      </c>
+      <c r="G44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Interest Payable</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>42603000</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>170480000</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>49826000</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>201103000</v>
+      </c>
+      <c r="F45" s="3" t="n"/>
+      <c r="G45" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>224277000</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>224823000</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>259430000</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>150008000</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>204312000</v>
+      </c>
+      <c r="G46" s="3" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Total Tax Payable</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>45020000</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>111560000</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>94664000</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>17063000</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>119572000</v>
+      </c>
+      <c r="G47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Income Tax Payable</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>45020000</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>111560000</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>94664000</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>17063000</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>119572000</v>
+      </c>
+      <c r="G48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>179257000</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>113263000</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>164766000</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>132945000</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>84740000</v>
+      </c>
+      <c r="G49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>46889027000</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>47237928000</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>48224461000</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>48230256000</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>23756517000</v>
+      </c>
+      <c r="G50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Total Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>41451809000</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>41864290000</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>42212359000</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>42634628000</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>6877488000</v>
+      </c>
+      <c r="G51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Other Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>1197086000</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>1186199000</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>1122693000</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>336212000</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>187126000</v>
+      </c>
+      <c r="G52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Assets</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>113642000</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>117386000</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>112159000</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>523923000</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>1898010000</v>
+      </c>
+      <c r="G53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Assets</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>113642000</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>117386000</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>112159000</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>97061000</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>1509159000</v>
+      </c>
+      <c r="G54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Non Current Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n"/>
+      <c r="C55" s="3" t="n"/>
+      <c r="D55" s="3" t="n"/>
+      <c r="E55" s="3" t="n">
+        <v>355802000</v>
+      </c>
+      <c r="F55" s="3" t="n"/>
+      <c r="G55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Goodwill And Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>38729225000</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>39170418000</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>39578806000</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>40025635000</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>3634666000</v>
+      </c>
+      <c r="G56" s="3" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>11875418000</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>12289529000</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>12679591000</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>13079912000</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>173394000</v>
+      </c>
+      <c r="G57" s="3" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>26853807000</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>26880889000</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>26899215000</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>26945723000</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>3461272000</v>
+      </c>
+      <c r="G58" s="3" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Net PPE</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>1411856000</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>1390287000</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>1398701000</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>1393056000</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>1157686000</v>
+      </c>
+      <c r="G59" s="3" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n"/>
+      <c r="C60" s="3" t="n"/>
+      <c r="D60" s="3" t="n">
+        <v>-965115000</v>
+      </c>
+      <c r="E60" s="3" t="n"/>
+      <c r="F60" s="3" t="n"/>
+      <c r="G60" s="3" t="n">
+        <v>-929981000</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Gross PPE</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>1411856000</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>1390287000</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>2363816000</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>1393056000</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>1157686000</v>
+      </c>
+      <c r="G61" s="3" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Leases</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n"/>
+      <c r="C62" s="3" t="n"/>
+      <c r="D62" s="3" t="n">
+        <v>295917000</v>
+      </c>
+      <c r="E62" s="3" t="n"/>
+      <c r="F62" s="3" t="n"/>
+      <c r="G62" s="3" t="n">
+        <v>271753000</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Other Properties</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>1411856000</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>1390287000</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>702008000</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>1393056000</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>1157686000</v>
+      </c>
+      <c r="G63" s="3" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Machinery Furniture Equipment</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n"/>
+      <c r="C64" s="3" t="n"/>
+      <c r="D64" s="3" t="n">
+        <v>1251987000</v>
+      </c>
+      <c r="E64" s="3" t="n"/>
+      <c r="F64" s="3" t="n"/>
+      <c r="G64" s="3" t="n">
+        <v>1099236000</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Buildings And Improvements</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n"/>
+      <c r="C65" s="3" t="n"/>
+      <c r="D65" s="3" t="n">
+        <v>100016000</v>
+      </c>
+      <c r="E65" s="3" t="n"/>
+      <c r="F65" s="3" t="n"/>
+      <c r="G65" s="3" t="n">
+        <v>103779000</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Land And Improvements</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n"/>
+      <c r="C66" s="3" t="n"/>
+      <c r="D66" s="3" t="n">
+        <v>13888000</v>
+      </c>
+      <c r="E66" s="3" t="n"/>
+      <c r="F66" s="3" t="n"/>
+      <c r="G66" s="3" t="n">
+        <v>18219000</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n"/>
+      <c r="C67" s="3" t="n"/>
+      <c r="D67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="3" t="n"/>
+      <c r="F67" s="3" t="n"/>
+      <c r="G67" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>5437218000</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>5373638000</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>6012102000</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>5595628000</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>16879029000</v>
+      </c>
+      <c r="G68" s="3" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Other Current Assets</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v>1195391000</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>1088118000</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>1180526000</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>1153172000</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>1217584000</v>
+      </c>
+      <c r="G69" s="3" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Assets Held For Sale Current</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>48248000</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>48152000</v>
+      </c>
+      <c r="D70" s="3" t="n"/>
+      <c r="E70" s="3" t="n">
+        <v>74317000</v>
+      </c>
+      <c r="F70" s="3" t="n"/>
+      <c r="G70" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v>441836000</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>393221000</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>365190000</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>382056000</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>395339000</v>
+      </c>
+      <c r="G71" s="3" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v>1267305000</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>1640665000</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>1505427000</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>1392373000</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>1002195000</v>
+      </c>
+      <c r="G72" s="3" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Receivables Adjustments Allowances</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n"/>
+      <c r="C73" s="3" t="n"/>
+      <c r="D73" s="3" t="n">
+        <v>-88959000</v>
+      </c>
+      <c r="E73" s="3" t="n"/>
+      <c r="F73" s="3" t="n"/>
+      <c r="G73" s="3" t="n">
+        <v>-51008000</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Other Receivables</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n"/>
+      <c r="C74" s="3" t="n"/>
+      <c r="D74" s="3" t="n">
+        <v>45528000</v>
+      </c>
+      <c r="E74" s="3" t="n"/>
+      <c r="F74" s="3" t="n"/>
+      <c r="G74" s="3" t="n">
+        <v>44166000</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v>1267305000</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>1640665000</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>1548858000</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>1392373000</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>1002195000</v>
+      </c>
+      <c r="G75" s="3" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Cash Cash Equivalents And Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="n">
+        <v>2484438000</v>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>2203482000</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>2960959000</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>2593710000</v>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>14263911000</v>
+      </c>
+      <c r="G76" s="3" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Other Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="n">
+        <v>71966000</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>73910000</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>72929000</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>67235000</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>144816000</v>
+      </c>
+      <c r="G77" s="3" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Cash And Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="n">
+        <v>2412472000</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>2129572000</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>2888030000</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>2526475000</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>14119095000</v>
+      </c>
+      <c r="G78" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6022,13 +8328,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:H57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6038,6 +8344,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6048,30 +8355,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-10-31</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-07-31</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-04-30</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2025-01-31</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024-10-31</t>
         </is>
@@ -6084,21 +8396,22 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>574736000</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>821512000</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>605192000</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>632355000</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>219777000</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>-108170000</v>
-      </c>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6111,7 +8424,8 @@
       <c r="D3" s="3" t="n"/>
       <c r="E3" s="3" t="n"/>
       <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n">
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6122,21 +8436,22 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>-11059000</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>-3451310000</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>-861058000</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>-1290000</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="F4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>-1289000</v>
-      </c>
       <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6145,15 +8460,16 @@
         </is>
       </c>
       <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n">
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>4294876000</v>
       </c>
-      <c r="E5" s="3" t="n"/>
       <c r="F5" s="3" t="n"/>
       <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6162,21 +8478,22 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>103394000</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>2012742000</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>90317000</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>19793000</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="F6" s="3" t="n">
         <v>103891000</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>14417000</v>
-      </c>
       <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6185,21 +8502,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>-54198000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>-35320000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>-34546000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>-38605000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>-55588000</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>-40715000</v>
-      </c>
       <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6208,21 +8526,22 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>2416757000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>2134314000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>2893721000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>2532170000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>14123433000</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>3657780000</v>
-      </c>
       <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6231,21 +8550,22 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>2134314000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>2893721000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>2532170000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>14123433000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>3657780000</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>3898729000</v>
-      </c>
       <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6254,21 +8574,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>-12679000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>3432000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>-6753000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>463000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>17862000</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>-9676000</v>
-      </c>
       <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6277,21 +8598,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>295122000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>-762839000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>368304000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>-11591726000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>10447791000</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>-231273000</v>
-      </c>
       <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6300,21 +8622,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>-280952000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>-1583165000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>-835851000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>4236997000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>10096449000</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>-141838000</v>
-      </c>
       <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6323,21 +8646,22 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>-280952000</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>-1583165000</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>-835851000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>4236997000</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>10096449000</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>-141838000</v>
-      </c>
       <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6346,21 +8670,22 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>-110787000</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>-144597000</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>-65110000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>-76382000</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>-41906000</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>-154966000</v>
-      </c>
       <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6369,21 +8694,22 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>-159106000</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>2012742000</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>90317000</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>19793000</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="F15" s="3" t="n">
         <v>103891000</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>14417000</v>
-      </c>
       <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6396,7 +8722,8 @@
       <c r="D16" s="3" t="n"/>
       <c r="E16" s="3" t="n"/>
       <c r="F16" s="3" t="n"/>
-      <c r="G16" s="3" t="n">
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6407,21 +8734,22 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
+        <v>103394000</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>2012742000</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="D17" s="3" t="n">
         <v>90317000</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>19793000</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="F17" s="3" t="n">
         <v>103891000</v>
       </c>
-      <c r="F17" s="3" t="n">
-        <v>14417000</v>
-      </c>
       <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6430,21 +8758,22 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
+        <v>-11059000</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>-3451310000</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>-861058000</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>4293586000</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="F18" s="3" t="n">
         <v>10034464000</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>-1289000</v>
-      </c>
       <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6453,21 +8782,22 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
+        <v>-11059000</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>-3451310000</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="D19" s="3" t="n">
         <v>-861058000</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>4293586000</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>10034464000</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>-1289000</v>
-      </c>
       <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -6476,21 +8806,22 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
+        <v>-11059000</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>-3451310000</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>-861058000</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>-1290000</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>-1289000</v>
-      </c>
       <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6499,15 +8830,16 @@
         </is>
       </c>
       <c r="B21" s="3" t="n"/>
-      <c r="C21" s="3" t="n">
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>4294876000</v>
       </c>
-      <c r="E21" s="3" t="n"/>
       <c r="F21" s="3" t="n"/>
       <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6516,21 +8848,22 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>-52860000</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>-36506000</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>564417000</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>-16499683000</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>75977000</v>
       </c>
-      <c r="F22" s="3" t="n">
-        <v>-21980000</v>
-      </c>
       <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -6539,21 +8872,22 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>-52860000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>-36506000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>564417000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>-16499683000</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>75977000</v>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>-21980000</v>
-      </c>
       <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6562,19 +8896,20 @@
         </is>
       </c>
       <c r="B24" s="3" t="n"/>
-      <c r="C24" s="3" t="n">
+      <c r="C24" s="3" t="n"/>
+      <c r="D24" s="3" t="n">
         <v>246000</v>
-      </c>
-      <c r="D24" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="E24" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3" t="n">
         <v>-611000</v>
       </c>
-      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6583,21 +8918,22 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
+        <v>1338000</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>-1186000</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="D25" s="3" t="n">
         <v>-5287000</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="E25" s="3" t="n">
         <v>147715000</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="F25" s="3" t="n">
         <v>11012000</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>-4462000</v>
-      </c>
       <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -6606,21 +8942,22 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
+        <v>11118000</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>3718000</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>12877000</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E26" s="3" t="n">
         <v>148433000</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="F26" s="3" t="n">
         <v>21381000</v>
       </c>
-      <c r="F26" s="3" t="n">
-        <v>36095000</v>
-      </c>
       <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6629,21 +8966,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
+        <v>-9780000</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>-4904000</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>-18164000</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="E27" s="3" t="n">
         <v>-718000</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="F27" s="3" t="n">
         <v>-10369000</v>
       </c>
-      <c r="F27" s="3" t="n">
-        <v>-40557000</v>
-      </c>
       <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6655,18 +8993,19 @@
         <v>0</v>
       </c>
       <c r="C28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="3" t="n">
         <v>604004000</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="E28" s="3" t="n">
         <v>-16608793000</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="F28" s="3" t="n">
         <v>46274000</v>
       </c>
-      <c r="F28" s="3" t="n">
-        <v>23808000</v>
-      </c>
       <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6678,18 +9017,19 @@
         <v>0</v>
       </c>
       <c r="C29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="3" t="n">
         <v>604004000</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>72464000</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>46274000</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>23808000</v>
-      </c>
       <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6698,14 +9038,12 @@
         </is>
       </c>
       <c r="B30" s="3" t="n"/>
-      <c r="C30" s="3" t="n">
+      <c r="C30" s="3" t="n"/>
+      <c r="D30" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="E30" s="3" t="n">
         <v>-16681257000</v>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>0</v>
@@ -6713,6 +9051,9 @@
       <c r="G30" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="H30" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6721,21 +9062,22 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
+        <v>-54198000</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>-35320000</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="D31" s="3" t="n">
         <v>-34546000</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>-38605000</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="F31" s="3" t="n">
         <v>18691000</v>
       </c>
-      <c r="F31" s="3" t="n">
-        <v>-40715000</v>
-      </c>
       <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6744,15 +9086,16 @@
         </is>
       </c>
       <c r="B32" s="3" t="n"/>
-      <c r="C32" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="C32" s="3" t="n"/>
       <c r="D32" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E32" s="3" t="n"/>
+      <c r="E32" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="F32" s="3" t="n"/>
       <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6761,21 +9104,22 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
+        <v>-54198000</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>-35320000</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="D33" s="3" t="n">
         <v>-34546000</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="E33" s="3" t="n">
         <v>-38605000</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="F33" s="3" t="n">
         <v>-55588000</v>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>-40715000</v>
-      </c>
       <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6788,7 +9132,8 @@
       <c r="D34" s="3" t="n"/>
       <c r="E34" s="3" t="n"/>
       <c r="F34" s="3" t="n"/>
-      <c r="G34" s="3" t="n">
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6799,21 +9144,22 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
+        <v>628934000</v>
+      </c>
+      <c r="C35" s="3" t="n">
         <v>856832000</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="D35" s="3" t="n">
         <v>639738000</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="E35" s="3" t="n">
         <v>670960000</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="F35" s="3" t="n">
         <v>275365000</v>
       </c>
-      <c r="F35" s="3" t="n">
-        <v>-67455000</v>
-      </c>
       <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -6822,21 +9168,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>628934000</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>856832000</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>639738000</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>670960000</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>275365000</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>-67455000</v>
-      </c>
       <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6845,21 +9192,22 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>-66794000</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>58215000</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>80164000</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>79065000</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="F37" s="3" t="n">
         <v>-137122000</v>
       </c>
-      <c r="F37" s="3" t="n">
-        <v>-518700000</v>
-      </c>
       <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -6868,21 +9216,22 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
+        <v>-208729000</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>282676000</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="D38" s="3" t="n">
         <v>401891000</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="E38" s="3" t="n">
         <v>-85997000</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="F38" s="3" t="n">
         <v>-64300000</v>
       </c>
-      <c r="F38" s="3" t="n">
-        <v>-9982000</v>
-      </c>
       <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6891,21 +9240,22 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
+        <v>-41821000</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>-32345000</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="D39" s="3" t="n">
         <v>-35243000</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="E39" s="3" t="n">
         <v>-29743000</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="F39" s="3" t="n">
         <v>-25515000</v>
       </c>
-      <c r="F39" s="3" t="n">
-        <v>-23102000</v>
-      </c>
       <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6914,21 +9264,22 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
+        <v>-5647000</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>-81413000</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>-53583000</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>-391735000</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="F40" s="3" t="n">
         <v>7436000</v>
       </c>
-      <c r="F40" s="3" t="n">
-        <v>-43494000</v>
-      </c>
       <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6937,21 +9288,22 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
+        <v>-77343000</v>
+      </c>
+      <c r="C41" s="3" t="n">
         <v>-37286000</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="D41" s="3" t="n">
         <v>-44871000</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="E41" s="3" t="n">
         <v>273913000</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="F41" s="3" t="n">
         <v>71122000</v>
       </c>
-      <c r="F41" s="3" t="n">
-        <v>-313651000</v>
-      </c>
       <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6960,21 +9312,22 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
+        <v>-39967000</v>
+      </c>
+      <c r="C42" s="3" t="n">
         <v>84616000</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="D42" s="3" t="n">
         <v>-53430000</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="E42" s="3" t="n">
         <v>260820000</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="F42" s="3" t="n">
         <v>-36905000</v>
       </c>
-      <c r="F42" s="3" t="n">
-        <v>-103567000</v>
-      </c>
       <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6983,21 +9336,22 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
+        <v>-56450000</v>
+      </c>
+      <c r="C43" s="3" t="n">
         <v>-29382000</v>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="D43" s="3" t="n">
         <v>11551000</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="E43" s="3" t="n">
         <v>5698000</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="F43" s="3" t="n">
         <v>16086000</v>
       </c>
-      <c r="F43" s="3" t="n">
-        <v>-55852000</v>
-      </c>
       <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -7006,21 +9360,22 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
+        <v>363163000</v>
+      </c>
+      <c r="C44" s="3" t="n">
         <v>-128651000</v>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="D44" s="3" t="n">
         <v>-146151000</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="E44" s="3" t="n">
         <v>46109000</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="F44" s="3" t="n">
         <v>-105046000</v>
       </c>
-      <c r="F44" s="3" t="n">
-        <v>30948000</v>
-      </c>
       <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -7029,21 +9384,22 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
+        <v>363163000</v>
+      </c>
+      <c r="C45" s="3" t="n">
         <v>-128651000</v>
       </c>
-      <c r="C45" s="3" t="n">
+      <c r="D45" s="3" t="n">
         <v>-146151000</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="E45" s="3" t="n">
         <v>46109000</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="F45" s="3" t="n">
         <v>-105046000</v>
       </c>
-      <c r="F45" s="3" t="n">
-        <v>30948000</v>
-      </c>
       <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -7052,21 +9408,22 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
+        <v>62701000</v>
+      </c>
+      <c r="C46" s="3" t="n">
         <v>68059000</v>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="D46" s="3" t="n">
         <v>57707000</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="E46" s="3" t="n">
         <v>48047000</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="F46" s="3" t="n">
         <v>-50525000</v>
       </c>
-      <c r="F46" s="3" t="n">
-        <v>48593000</v>
-      </c>
       <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -7075,21 +9432,22 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
+        <v>222303000</v>
+      </c>
+      <c r="C47" s="3" t="n">
         <v>258724000</v>
       </c>
-      <c r="C47" s="3" t="n">
+      <c r="D47" s="3" t="n">
         <v>237385000</v>
       </c>
-      <c r="D47" s="3" t="n">
+      <c r="E47" s="3" t="n">
         <v>267723000</v>
       </c>
-      <c r="E47" s="3" t="n">
+      <c r="F47" s="3" t="n">
         <v>201723000</v>
       </c>
-      <c r="F47" s="3" t="n">
-        <v>186463000</v>
-      </c>
       <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -7098,21 +9456,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
+        <v>6636000</v>
+      </c>
+      <c r="C48" s="3" t="n">
         <v>8206000</v>
       </c>
-      <c r="C48" s="3" t="n">
+      <c r="D48" s="3" t="n">
         <v>27332000</v>
       </c>
-      <c r="D48" s="3" t="n">
+      <c r="E48" s="3" t="n">
         <v>7619000</v>
       </c>
-      <c r="E48" s="3" t="n">
+      <c r="F48" s="3" t="n">
         <v>6021000</v>
       </c>
-      <c r="F48" s="3" t="n">
-        <v>9919000</v>
-      </c>
       <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -7121,21 +9480,22 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
+        <v>-69269000</v>
+      </c>
+      <c r="C49" s="3" t="n">
         <v>-51776000</v>
       </c>
-      <c r="C49" s="3" t="n">
+      <c r="D49" s="3" t="n">
         <v>-144083000</v>
       </c>
-      <c r="D49" s="3" t="n">
+      <c r="E49" s="3" t="n">
         <v>-89440000</v>
       </c>
-      <c r="E49" s="3" t="n">
+      <c r="F49" s="3" t="n">
         <v>-98095000</v>
       </c>
-      <c r="F49" s="3" t="n">
-        <v>-139075000</v>
-      </c>
       <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -7144,21 +9504,22 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
+        <v>-69269000</v>
+      </c>
+      <c r="C50" s="3" t="n">
         <v>-51776000</v>
       </c>
-      <c r="C50" s="3" t="n">
+      <c r="D50" s="3" t="n">
         <v>-144083000</v>
       </c>
-      <c r="D50" s="3" t="n">
+      <c r="E50" s="3" t="n">
         <v>-89440000</v>
       </c>
-      <c r="E50" s="3" t="n">
+      <c r="F50" s="3" t="n">
         <v>-98095000</v>
       </c>
-      <c r="F50" s="3" t="n">
-        <v>-139075000</v>
-      </c>
       <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -7167,21 +9528,22 @@
         </is>
       </c>
       <c r="B51" s="3" t="n">
+        <v>456489000</v>
+      </c>
+      <c r="C51" s="3" t="n">
         <v>450688000</v>
       </c>
-      <c r="C51" s="3" t="n">
+      <c r="D51" s="3" t="n">
         <v>449123000</v>
       </c>
-      <c r="D51" s="3" t="n">
+      <c r="E51" s="3" t="n">
         <v>114469000</v>
       </c>
-      <c r="E51" s="3" t="n">
+      <c r="F51" s="3" t="n">
         <v>48904000</v>
       </c>
-      <c r="F51" s="3" t="n">
-        <v>47934000</v>
-      </c>
       <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -7190,21 +9552,22 @@
         </is>
       </c>
       <c r="B52" s="3" t="n">
+        <v>456489000</v>
+      </c>
+      <c r="C52" s="3" t="n">
         <v>450688000</v>
       </c>
-      <c r="C52" s="3" t="n">
+      <c r="D52" s="3" t="n">
         <v>449123000</v>
       </c>
-      <c r="D52" s="3" t="n">
+      <c r="E52" s="3" t="n">
         <v>114469000</v>
       </c>
-      <c r="E52" s="3" t="n">
+      <c r="F52" s="3" t="n">
         <v>48904000</v>
       </c>
-      <c r="F52" s="3" t="n">
-        <v>47934000</v>
-      </c>
       <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -7213,15 +9576,16 @@
         </is>
       </c>
       <c r="B53" s="3" t="n"/>
-      <c r="C53" s="3" t="n">
+      <c r="C53" s="3" t="n"/>
+      <c r="D53" s="3" t="n">
         <v>-516343000</v>
       </c>
-      <c r="D53" s="3" t="n">
+      <c r="E53" s="3" t="n">
         <v>1200000</v>
       </c>
-      <c r="E53" s="3" t="n"/>
       <c r="F53" s="3" t="n"/>
-      <c r="G53" s="3" t="n">
+      <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n">
         <v>-868830000</v>
       </c>
     </row>
@@ -7232,15 +9596,16 @@
         </is>
       </c>
       <c r="B54" s="3" t="n"/>
-      <c r="C54" s="3" t="n">
+      <c r="C54" s="3" t="n"/>
+      <c r="D54" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D54" s="3" t="n">
+      <c r="E54" s="3" t="n">
         <v>1200000</v>
       </c>
-      <c r="E54" s="3" t="n"/>
       <c r="F54" s="3" t="n"/>
-      <c r="G54" s="3" t="n">
+      <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7251,15 +9616,16 @@
         </is>
       </c>
       <c r="B55" s="3" t="n"/>
-      <c r="C55" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="C55" s="3" t="n"/>
       <c r="D55" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E55" s="3" t="n"/>
+      <c r="E55" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="F55" s="3" t="n"/>
       <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -7268,15 +9634,16 @@
         </is>
       </c>
       <c r="B56" s="3" t="n"/>
-      <c r="C56" s="3" t="n">
+      <c r="C56" s="3" t="n"/>
+      <c r="D56" s="3" t="n">
         <v>-516343000</v>
       </c>
-      <c r="D56" s="3" t="n">
+      <c r="E56" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E56" s="3" t="n"/>
       <c r="F56" s="3" t="n"/>
       <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -7285,28 +9652,29 @@
         </is>
       </c>
       <c r="B57" s="3" t="n">
+        <v>16868000</v>
+      </c>
+      <c r="C57" s="3" t="n">
         <v>64716000</v>
       </c>
-      <c r="C57" s="3" t="n">
+      <c r="D57" s="3" t="n">
         <v>448453000</v>
       </c>
-      <c r="D57" s="3" t="n">
+      <c r="E57" s="3" t="n">
         <v>242277000</v>
       </c>
-      <c r="E57" s="3" t="n">
+      <c r="F57" s="3" t="n">
         <v>345110000</v>
       </c>
-      <c r="F57" s="3" t="n">
-        <v>297411000</v>
-      </c>
       <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7334,12 +9702,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Gross margin</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>no gaps detected</t>
+          <t>GAAP (statement) ~73% vs yfinance info.grossMargins 83% — info is a non-GAAP basis; FY Summary uses GAAP</t>
         </is>
       </c>
     </row>
